--- a/testdata/testdata.xlsx
+++ b/testdata/testdata.xlsx
@@ -1,31 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/10573e7fdf6d9d5c/Desktop/PlaywrightProject/testdata/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC1048E6A11972425ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA4B768C-048A-4267-8A7C-547B1B58211E}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_AA29BBFD9A25EE58903BA1FEA760DEF7103EE7A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{055A0A54-3AB7-4CA1-AE8C-CB27B26F7CD1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="flipkart_products" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>Name</t>
   </si>
@@ -40,6 +31,129 @@
   </si>
   <si>
     <t>John</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Prices</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy A55 5G (Awesome Iceblue, 128 GB)</t>
+  </si>
+  <si>
+    <t>₹25,308</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy A55 5G (Awesome Navy, 128 GB)</t>
+  </si>
+  <si>
+    <t>₹24,553</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy A55 5G (Awesome Iceblue, 256 GB)</t>
+  </si>
+  <si>
+    <t>₹27,799</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy A55 5G (Awesome Navy, 256 GB)</t>
+  </si>
+  <si>
+    <t>₹26,983</t>
+  </si>
+  <si>
+    <t>₹30,990</t>
+  </si>
+  <si>
+    <t>₹34,975</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy F55 5G (Raisin Black, 256 GB)</t>
+  </si>
+  <si>
+    <t>₹21,989</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy M55 5G (Light Green, 256 GB)</t>
+  </si>
+  <si>
+    <t>₹23,349</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy F55 5G (Apricot Crush, 128 GB)</t>
+  </si>
+  <si>
+    <t>₹20,030</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy M55 5G (Danim Black, 256 GB)</t>
+  </si>
+  <si>
+    <t>₹26,800</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy S24 5G Snapdragon (Amber Yellow, 128 GB)</t>
+  </si>
+  <si>
+    <t>₹39,999</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy S24 5G Snapdragon (Cobalt Violet, 128 GB)</t>
+  </si>
+  <si>
+    <t>Samsung M55s (Thunder Black, 128 GB)</t>
+  </si>
+  <si>
+    <t>₹18,588</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy F55 5G (Apricot Crush, 256 GB)</t>
+  </si>
+  <si>
+    <t>₹31,999</t>
+  </si>
+  <si>
+    <t>VRAVMO SM-A556V GALAXY A55 5G (MAIN FLEX) LCD Flex Cable</t>
+  </si>
+  <si>
+    <t>₹405</t>
+  </si>
+  <si>
+    <t>SeriousShopper SAMSUNG GALAXY A55 5G Back Panel</t>
+  </si>
+  <si>
+    <t>₹650</t>
+  </si>
+  <si>
+    <t>₹29,924</t>
+  </si>
+  <si>
+    <t>₹34,999</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy F55 5G (Raisin Black, 128 GB)</t>
+  </si>
+  <si>
+    <t>₹18,490</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy M55 5G (Denim Black / Black, 128 GB)</t>
+  </si>
+  <si>
+    <t>₹18,099</t>
+  </si>
+  <si>
+    <t>VRAVMO SAMSUNG GALAXY A55 5G (BLUE) Back Panel</t>
+  </si>
+  <si>
+    <t>₹619</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy M55 5G (Denim Black / Black, 256 GB)</t>
+  </si>
+  <si>
+    <t>₹23,490</t>
   </si>
 </sst>
 </file>
@@ -358,9 +472,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -368,7 +482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -376,7 +490,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -384,7 +498,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -395,4 +509,219 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
 </file>